--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124990391</v>
+        <v>124988719</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611049</v>
+        <v>610977</v>
       </c>
       <c r="R2" t="n">
-        <v>6954095</v>
+        <v>6953915</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124986151</v>
+        <v>124990391</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611162</v>
+        <v>611049</v>
       </c>
       <c r="R3" t="n">
-        <v>6953998</v>
+        <v>6954095</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986592</v>
+        <v>124987437</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611110</v>
+        <v>611077</v>
       </c>
       <c r="R4" t="n">
-        <v>6953986</v>
+        <v>6953924</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987437</v>
+        <v>124986151</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611077</v>
+        <v>611162</v>
       </c>
       <c r="R5" t="n">
-        <v>6953924</v>
+        <v>6953998</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124985975</v>
+        <v>124989858</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1110,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611188</v>
+        <v>611048</v>
       </c>
       <c r="R6" t="n">
-        <v>6954015</v>
+        <v>6954042</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987900</v>
+        <v>124987406</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,7 +1253,7 @@
         <v>611079</v>
       </c>
       <c r="R7" t="n">
-        <v>6953885</v>
+        <v>6953923</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987571</v>
+        <v>124987900</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611100</v>
+        <v>611079</v>
       </c>
       <c r="R8" t="n">
-        <v>6953896</v>
+        <v>6953885</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987406</v>
+        <v>124988003</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,7 +1457,7 @@
         <v>611079</v>
       </c>
       <c r="R9" t="n">
-        <v>6953923</v>
+        <v>6953866</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124989858</v>
+        <v>124989524</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,43 +1528,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611048</v>
+        <v>611045</v>
       </c>
       <c r="R10" t="n">
-        <v>6954042</v>
+        <v>6954010</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1587,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987074</v>
+        <v>124986592</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611078</v>
+        <v>611110</v>
       </c>
       <c r="R11" t="n">
-        <v>6953994</v>
+        <v>6953986</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987778</v>
+        <v>124988911</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611077</v>
+        <v>611003</v>
       </c>
       <c r="R12" t="n">
-        <v>6953888</v>
+        <v>6953895</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124986204</v>
+        <v>124987571</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611165</v>
+        <v>611100</v>
       </c>
       <c r="R13" t="n">
-        <v>6954011</v>
+        <v>6953896</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988719</v>
+        <v>124987461</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610977</v>
+        <v>611070</v>
       </c>
       <c r="R14" t="n">
         <v>6953915</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987461</v>
+        <v>124986907</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611070</v>
+        <v>611061</v>
       </c>
       <c r="R15" t="n">
-        <v>6953915</v>
+        <v>6953941</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124986907</v>
+        <v>124987778</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611061</v>
+        <v>611077</v>
       </c>
       <c r="R16" t="n">
-        <v>6953941</v>
+        <v>6953888</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988911</v>
+        <v>124986204</v>
       </c>
       <c r="B17" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611003</v>
+        <v>611165</v>
       </c>
       <c r="R17" t="n">
-        <v>6953895</v>
+        <v>6954011</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124989524</v>
+        <v>124987074</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611045</v>
+        <v>611078</v>
       </c>
       <c r="R18" t="n">
-        <v>6954010</v>
+        <v>6953994</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124988003</v>
+        <v>124985975</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611079</v>
+        <v>611188</v>
       </c>
       <c r="R19" t="n">
-        <v>6953866</v>
+        <v>6954015</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124988719</v>
+        <v>124989524</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610977</v>
+        <v>611045</v>
       </c>
       <c r="R2" t="n">
-        <v>6953915</v>
+        <v>6954010</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124990391</v>
+        <v>124987461</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611049</v>
+        <v>611070</v>
       </c>
       <c r="R3" t="n">
-        <v>6954095</v>
+        <v>6953915</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987437</v>
+        <v>124990391</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611077</v>
+        <v>611049</v>
       </c>
       <c r="R4" t="n">
-        <v>6953924</v>
+        <v>6954095</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124986151</v>
+        <v>124987778</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611162</v>
+        <v>611077</v>
       </c>
       <c r="R5" t="n">
-        <v>6953998</v>
+        <v>6953888</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989858</v>
+        <v>124988719</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,43 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611048</v>
+        <v>610977</v>
       </c>
       <c r="R6" t="n">
-        <v>6954042</v>
+        <v>6953915</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987406</v>
+        <v>124988911</v>
       </c>
       <c r="B7" t="n">
         <v>91299</v>
@@ -1250,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611079</v>
+        <v>611003</v>
       </c>
       <c r="R7" t="n">
-        <v>6953923</v>
+        <v>6953895</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987900</v>
+        <v>124987571</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611079</v>
+        <v>611100</v>
       </c>
       <c r="R8" t="n">
-        <v>6953885</v>
+        <v>6953896</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124988003</v>
+        <v>124989858</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611079</v>
+        <v>611048</v>
       </c>
       <c r="R9" t="n">
-        <v>6953866</v>
+        <v>6954042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1490,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124989524</v>
+        <v>124986592</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>82597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611045</v>
+        <v>611110</v>
       </c>
       <c r="R10" t="n">
-        <v>6954010</v>
+        <v>6953986</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986592</v>
+        <v>124987074</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611110</v>
+        <v>611078</v>
       </c>
       <c r="R11" t="n">
-        <v>6953986</v>
+        <v>6953994</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988911</v>
+        <v>124986204</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611003</v>
+        <v>611165</v>
       </c>
       <c r="R12" t="n">
-        <v>6953895</v>
+        <v>6954011</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987571</v>
+        <v>124987406</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611100</v>
+        <v>611079</v>
       </c>
       <c r="R13" t="n">
-        <v>6953896</v>
+        <v>6953923</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1924,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987461</v>
+        <v>124987900</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611070</v>
+        <v>611079</v>
       </c>
       <c r="R14" t="n">
-        <v>6953915</v>
+        <v>6953885</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124986907</v>
+        <v>124988003</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611061</v>
+        <v>611079</v>
       </c>
       <c r="R15" t="n">
-        <v>6953941</v>
+        <v>6953866</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987778</v>
+        <v>124986907</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611077</v>
+        <v>611061</v>
       </c>
       <c r="R16" t="n">
-        <v>6953888</v>
+        <v>6953941</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986204</v>
+        <v>124985975</v>
       </c>
       <c r="B17" t="n">
         <v>90977</v>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611165</v>
+        <v>611188</v>
       </c>
       <c r="R17" t="n">
-        <v>6954011</v>
+        <v>6954015</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124987074</v>
+        <v>124986151</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,34 +2343,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611078</v>
+        <v>611162</v>
       </c>
       <c r="R18" t="n">
-        <v>6953994</v>
+        <v>6953998</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124985975</v>
+        <v>124987437</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611188</v>
+        <v>611077</v>
       </c>
       <c r="R19" t="n">
-        <v>6954015</v>
+        <v>6953924</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124986907</v>
+        <v>124985975</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611061</v>
+        <v>611188</v>
       </c>
       <c r="R16" t="n">
-        <v>6953941</v>
+        <v>6954015</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124985975</v>
+        <v>124986907</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611188</v>
+        <v>611061</v>
       </c>
       <c r="R17" t="n">
-        <v>6954015</v>
+        <v>6953941</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124989524</v>
+        <v>124990391</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611045</v>
+        <v>611049</v>
       </c>
       <c r="R2" t="n">
-        <v>6954010</v>
+        <v>6954095</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987461</v>
+        <v>124987778</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611070</v>
+        <v>611077</v>
       </c>
       <c r="R3" t="n">
-        <v>6953915</v>
+        <v>6953888</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124990391</v>
+        <v>124986592</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611049</v>
+        <v>611110</v>
       </c>
       <c r="R4" t="n">
-        <v>6954095</v>
+        <v>6953986</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987778</v>
+        <v>124986204</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611077</v>
+        <v>611165</v>
       </c>
       <c r="R5" t="n">
-        <v>6953888</v>
+        <v>6954011</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124988719</v>
+        <v>124987461</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610977</v>
+        <v>611070</v>
       </c>
       <c r="R6" t="n">
         <v>6953915</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988911</v>
+        <v>124986907</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611003</v>
+        <v>611061</v>
       </c>
       <c r="R7" t="n">
-        <v>6953895</v>
+        <v>6953941</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987571</v>
+        <v>124987406</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611100</v>
+        <v>611079</v>
       </c>
       <c r="R8" t="n">
-        <v>6953896</v>
+        <v>6953923</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124989858</v>
+        <v>124987437</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1415,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611048</v>
+        <v>611077</v>
       </c>
       <c r="R9" t="n">
-        <v>6954042</v>
+        <v>6953924</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1480,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986592</v>
+        <v>124986151</v>
       </c>
       <c r="B10" t="n">
-        <v>82597</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611110</v>
+        <v>611162</v>
       </c>
       <c r="R10" t="n">
-        <v>6953986</v>
+        <v>6953998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987074</v>
+        <v>124988911</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611078</v>
+        <v>611003</v>
       </c>
       <c r="R11" t="n">
-        <v>6953994</v>
+        <v>6953895</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124986204</v>
+        <v>124987571</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611165</v>
+        <v>611100</v>
       </c>
       <c r="R12" t="n">
-        <v>6954011</v>
+        <v>6953896</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987406</v>
+        <v>124985975</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611079</v>
+        <v>611188</v>
       </c>
       <c r="R13" t="n">
-        <v>6953923</v>
+        <v>6954015</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987900</v>
+        <v>124988719</v>
       </c>
       <c r="B14" t="n">
         <v>90977</v>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611079</v>
+        <v>610977</v>
       </c>
       <c r="R14" t="n">
-        <v>6953885</v>
+        <v>6953915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124988003</v>
+        <v>124987074</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611079</v>
+        <v>611078</v>
       </c>
       <c r="R15" t="n">
-        <v>6953866</v>
+        <v>6953994</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124985975</v>
+        <v>124989524</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611188</v>
+        <v>611045</v>
       </c>
       <c r="R16" t="n">
-        <v>6954015</v>
+        <v>6954010</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986907</v>
+        <v>124988003</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611061</v>
+        <v>611079</v>
       </c>
       <c r="R17" t="n">
-        <v>6953941</v>
+        <v>6953866</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124986151</v>
+        <v>124987900</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,43 +2334,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611162</v>
+        <v>611079</v>
       </c>
       <c r="R18" t="n">
-        <v>6953998</v>
+        <v>6953885</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124987437</v>
+        <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611077</v>
+        <v>611048</v>
       </c>
       <c r="R19" t="n">
-        <v>6953924</v>
+        <v>6954042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2510,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124986204</v>
+        <v>124987461</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611165</v>
+        <v>611070</v>
       </c>
       <c r="R5" t="n">
-        <v>6954011</v>
+        <v>6953915</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987461</v>
+        <v>124986907</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611070</v>
+        <v>611061</v>
       </c>
       <c r="R6" t="n">
-        <v>6953915</v>
+        <v>6953941</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124986907</v>
+        <v>124986204</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611061</v>
+        <v>611165</v>
       </c>
       <c r="R7" t="n">
-        <v>6953941</v>
+        <v>6954011</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988003</v>
+        <v>124987900</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
         <v>611079</v>
       </c>
       <c r="R17" t="n">
-        <v>6953866</v>
+        <v>6953885</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124987900</v>
+        <v>124988003</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
         <v>611079</v>
       </c>
       <c r="R18" t="n">
-        <v>6953885</v>
+        <v>6953866</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124990391</v>
+        <v>124986204</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611049</v>
+        <v>611165</v>
       </c>
       <c r="R2" t="n">
-        <v>6954095</v>
+        <v>6954011</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987778</v>
+        <v>124987571</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611077</v>
+        <v>611100</v>
       </c>
       <c r="R3" t="n">
-        <v>6953888</v>
+        <v>6953896</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986592</v>
+        <v>124987074</v>
       </c>
       <c r="B4" t="n">
-        <v>82597</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611110</v>
+        <v>611078</v>
       </c>
       <c r="R4" t="n">
-        <v>6953986</v>
+        <v>6953994</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987461</v>
+        <v>124989524</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611070</v>
+        <v>611045</v>
       </c>
       <c r="R5" t="n">
-        <v>6953915</v>
+        <v>6954010</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124986907</v>
+        <v>124988911</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611061</v>
+        <v>611003</v>
       </c>
       <c r="R6" t="n">
-        <v>6953941</v>
+        <v>6953895</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124986204</v>
+        <v>124988719</v>
       </c>
       <c r="B7" t="n">
         <v>90977</v>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611165</v>
+        <v>610977</v>
       </c>
       <c r="R7" t="n">
-        <v>6954011</v>
+        <v>6953915</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987406</v>
+        <v>124987437</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611079</v>
+        <v>611077</v>
       </c>
       <c r="R8" t="n">
-        <v>6953923</v>
+        <v>6953924</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987437</v>
+        <v>124987900</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R9" t="n">
-        <v>6953924</v>
+        <v>6953885</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986151</v>
+        <v>124986592</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>82597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611162</v>
+        <v>611110</v>
       </c>
       <c r="R10" t="n">
-        <v>6953998</v>
+        <v>6953986</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1608,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124988911</v>
+        <v>124989858</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,34 +1609,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611003</v>
+        <v>611048</v>
       </c>
       <c r="R11" t="n">
-        <v>6953895</v>
+        <v>6954042</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987571</v>
+        <v>124990391</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,34 +1721,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611100</v>
+        <v>611049</v>
       </c>
       <c r="R12" t="n">
-        <v>6953896</v>
+        <v>6954095</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124985975</v>
+        <v>124988003</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611188</v>
+        <v>611079</v>
       </c>
       <c r="R13" t="n">
-        <v>6954015</v>
+        <v>6953866</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124988719</v>
+        <v>124986907</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610977</v>
+        <v>611061</v>
       </c>
       <c r="R14" t="n">
-        <v>6953915</v>
+        <v>6953941</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987074</v>
+        <v>124987406</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611078</v>
+        <v>611079</v>
       </c>
       <c r="R15" t="n">
-        <v>6953994</v>
+        <v>6953923</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124989524</v>
+        <v>124987778</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611045</v>
+        <v>611077</v>
       </c>
       <c r="R16" t="n">
-        <v>6954010</v>
+        <v>6953888</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124987900</v>
+        <v>124986151</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2237,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611079</v>
+        <v>611162</v>
       </c>
       <c r="R17" t="n">
-        <v>6953885</v>
+        <v>6953998</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988003</v>
+        <v>124985975</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611079</v>
+        <v>611188</v>
       </c>
       <c r="R18" t="n">
-        <v>6953866</v>
+        <v>6954015</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2424,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124989858</v>
+        <v>124987461</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,39 +2450,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611048</v>
+        <v>611070</v>
       </c>
       <c r="R19" t="n">
-        <v>6954042</v>
+        <v>6953915</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,11 +2510,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124986204</v>
+        <v>124987778</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611165</v>
+        <v>611077</v>
       </c>
       <c r="R2" t="n">
-        <v>6954011</v>
+        <v>6953888</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987571</v>
+        <v>124988719</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611100</v>
+        <v>610977</v>
       </c>
       <c r="R3" t="n">
-        <v>6953896</v>
+        <v>6953915</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987074</v>
+        <v>124987900</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611078</v>
+        <v>611079</v>
       </c>
       <c r="R4" t="n">
-        <v>6953994</v>
+        <v>6953885</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989524</v>
+        <v>124989858</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611045</v>
+        <v>611048</v>
       </c>
       <c r="R5" t="n">
-        <v>6954010</v>
+        <v>6954042</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124988911</v>
+        <v>124987571</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611003</v>
+        <v>611100</v>
       </c>
       <c r="R6" t="n">
-        <v>6953895</v>
+        <v>6953896</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988719</v>
+        <v>124987074</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610977</v>
+        <v>611078</v>
       </c>
       <c r="R7" t="n">
-        <v>6953915</v>
+        <v>6953994</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987437</v>
+        <v>124988911</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611077</v>
+        <v>611003</v>
       </c>
       <c r="R8" t="n">
-        <v>6953924</v>
+        <v>6953895</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987900</v>
+        <v>124989524</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611079</v>
+        <v>611045</v>
       </c>
       <c r="R9" t="n">
-        <v>6953885</v>
+        <v>6954010</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986592</v>
+        <v>124987406</v>
       </c>
       <c r="B10" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611110</v>
+        <v>611079</v>
       </c>
       <c r="R10" t="n">
-        <v>6953986</v>
+        <v>6953923</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124989858</v>
+        <v>124990391</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1638,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611048</v>
+        <v>611049</v>
       </c>
       <c r="R11" t="n">
-        <v>6954042</v>
+        <v>6954095</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124990391</v>
+        <v>124985975</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,43 +1727,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611049</v>
+        <v>611188</v>
       </c>
       <c r="R12" t="n">
-        <v>6954095</v>
+        <v>6954015</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988003</v>
+        <v>124987437</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611079</v>
+        <v>611077</v>
       </c>
       <c r="R13" t="n">
-        <v>6953866</v>
+        <v>6953924</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987406</v>
+        <v>124986204</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611079</v>
+        <v>611165</v>
       </c>
       <c r="R15" t="n">
-        <v>6953923</v>
+        <v>6954011</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987778</v>
+        <v>124987461</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611077</v>
+        <v>611070</v>
       </c>
       <c r="R16" t="n">
-        <v>6953888</v>
+        <v>6953915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124985975</v>
+        <v>124986592</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611188</v>
+        <v>611110</v>
       </c>
       <c r="R18" t="n">
-        <v>6954015</v>
+        <v>6953986</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124987461</v>
+        <v>124988003</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611070</v>
+        <v>611079</v>
       </c>
       <c r="R19" t="n">
-        <v>6953915</v>
+        <v>6953866</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124988719</v>
+        <v>124989858</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610977</v>
+        <v>611048</v>
       </c>
       <c r="R3" t="n">
-        <v>6953915</v>
+        <v>6954042</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987900</v>
+        <v>124988719</v>
       </c>
       <c r="B4" t="n">
         <v>90977</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611079</v>
+        <v>610977</v>
       </c>
       <c r="R4" t="n">
-        <v>6953885</v>
+        <v>6953915</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989858</v>
+        <v>124987900</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611048</v>
+        <v>611079</v>
       </c>
       <c r="R5" t="n">
-        <v>6954042</v>
+        <v>6953885</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987074</v>
+        <v>124989524</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611078</v>
+        <v>611045</v>
       </c>
       <c r="R7" t="n">
-        <v>6953994</v>
+        <v>6954010</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124988911</v>
+        <v>124987074</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>88359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611003</v>
+        <v>611078</v>
       </c>
       <c r="R8" t="n">
-        <v>6953895</v>
+        <v>6953994</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124989524</v>
+        <v>124988911</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611045</v>
+        <v>611003</v>
       </c>
       <c r="R9" t="n">
-        <v>6954010</v>
+        <v>6953895</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987778</v>
+        <v>124987900</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R2" t="n">
-        <v>6953888</v>
+        <v>6953885</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124989858</v>
+        <v>124987571</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611048</v>
+        <v>611100</v>
       </c>
       <c r="R3" t="n">
-        <v>6954042</v>
+        <v>6953896</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124988719</v>
+        <v>124986204</v>
       </c>
       <c r="B4" t="n">
         <v>90977</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610977</v>
+        <v>611165</v>
       </c>
       <c r="R4" t="n">
-        <v>6953915</v>
+        <v>6954011</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987900</v>
+        <v>124990391</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611079</v>
+        <v>611049</v>
       </c>
       <c r="R5" t="n">
-        <v>6953885</v>
+        <v>6954095</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987571</v>
+        <v>124988003</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611100</v>
+        <v>611079</v>
       </c>
       <c r="R6" t="n">
-        <v>6953896</v>
+        <v>6953866</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124989524</v>
+        <v>124985975</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611045</v>
+        <v>611188</v>
       </c>
       <c r="R7" t="n">
-        <v>6954010</v>
+        <v>6954015</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987074</v>
+        <v>124989858</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611078</v>
+        <v>611048</v>
       </c>
       <c r="R8" t="n">
-        <v>6953994</v>
+        <v>6954042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987406</v>
+        <v>124987461</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611079</v>
+        <v>611070</v>
       </c>
       <c r="R10" t="n">
-        <v>6953923</v>
+        <v>6953915</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124990391</v>
+        <v>124987074</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,39 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611049</v>
+        <v>611078</v>
       </c>
       <c r="R11" t="n">
-        <v>6954095</v>
+        <v>6953994</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124985975</v>
+        <v>124987778</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611188</v>
+        <v>611077</v>
       </c>
       <c r="R12" t="n">
-        <v>6954015</v>
+        <v>6953888</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124986907</v>
+        <v>124989524</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611061</v>
+        <v>611045</v>
       </c>
       <c r="R14" t="n">
-        <v>6953941</v>
+        <v>6954010</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124986204</v>
+        <v>124987406</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611165</v>
+        <v>611079</v>
       </c>
       <c r="R15" t="n">
-        <v>6954011</v>
+        <v>6953923</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987461</v>
+        <v>124988719</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611070</v>
+        <v>610977</v>
       </c>
       <c r="R16" t="n">
         <v>6953915</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986151</v>
+        <v>124986907</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,39 +2241,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611162</v>
+        <v>611061</v>
       </c>
       <c r="R17" t="n">
-        <v>6953998</v>
+        <v>6953941</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2434,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124988003</v>
+        <v>124986151</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,34 +2445,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611079</v>
+        <v>611162</v>
       </c>
       <c r="R19" t="n">
-        <v>6953866</v>
+        <v>6953998</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987900</v>
+        <v>124987437</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611079</v>
+        <v>611077</v>
       </c>
       <c r="R2" t="n">
-        <v>6953885</v>
+        <v>6953924</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124987571</v>
+        <v>124989858</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611100</v>
+        <v>611048</v>
       </c>
       <c r="R3" t="n">
-        <v>6953896</v>
+        <v>6954042</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986204</v>
+        <v>124990391</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611165</v>
+        <v>611049</v>
       </c>
       <c r="R4" t="n">
-        <v>6954011</v>
+        <v>6954095</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124990391</v>
+        <v>124989524</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,43 +1013,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611049</v>
+        <v>611045</v>
       </c>
       <c r="R5" t="n">
-        <v>6954095</v>
+        <v>6954010</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124988003</v>
+        <v>124987406</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,7 +1146,7 @@
         <v>611079</v>
       </c>
       <c r="R6" t="n">
-        <v>6953866</v>
+        <v>6953923</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124985975</v>
+        <v>124988719</v>
       </c>
       <c r="B7" t="n">
         <v>90977</v>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611188</v>
+        <v>610977</v>
       </c>
       <c r="R7" t="n">
-        <v>6954015</v>
+        <v>6953915</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124989858</v>
+        <v>124986204</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,43 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611048</v>
+        <v>611165</v>
       </c>
       <c r="R8" t="n">
-        <v>6954042</v>
+        <v>6954011</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124988911</v>
+        <v>124985975</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611003</v>
+        <v>611188</v>
       </c>
       <c r="R9" t="n">
-        <v>6953895</v>
+        <v>6954015</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987461</v>
+        <v>124988003</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611070</v>
+        <v>611079</v>
       </c>
       <c r="R10" t="n">
-        <v>6953915</v>
+        <v>6953866</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987074</v>
+        <v>124986907</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611078</v>
+        <v>611061</v>
       </c>
       <c r="R11" t="n">
-        <v>6953994</v>
+        <v>6953941</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987778</v>
+        <v>124987571</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611077</v>
+        <v>611100</v>
       </c>
       <c r="R12" t="n">
-        <v>6953888</v>
+        <v>6953896</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987437</v>
+        <v>124987900</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R13" t="n">
-        <v>6953924</v>
+        <v>6953885</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124989524</v>
+        <v>124987074</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>88359</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611045</v>
+        <v>611078</v>
       </c>
       <c r="R14" t="n">
-        <v>6954010</v>
+        <v>6953994</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987406</v>
+        <v>124986592</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611079</v>
+        <v>611110</v>
       </c>
       <c r="R15" t="n">
-        <v>6953923</v>
+        <v>6953986</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124988719</v>
+        <v>124988911</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610977</v>
+        <v>611003</v>
       </c>
       <c r="R16" t="n">
-        <v>6953915</v>
+        <v>6953895</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124986907</v>
+        <v>124987461</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611061</v>
+        <v>611070</v>
       </c>
       <c r="R17" t="n">
-        <v>6953941</v>
+        <v>6953915</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124986592</v>
+        <v>124987778</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611110</v>
+        <v>611077</v>
       </c>
       <c r="R18" t="n">
-        <v>6953986</v>
+        <v>6953888</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987437</v>
+        <v>124986907</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611077</v>
+        <v>611061</v>
       </c>
       <c r="R2" t="n">
-        <v>6953924</v>
+        <v>6953941</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124989858</v>
+        <v>124989524</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611048</v>
+        <v>611045</v>
       </c>
       <c r="R3" t="n">
-        <v>6954042</v>
+        <v>6954010</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124990391</v>
+        <v>124987406</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611049</v>
+        <v>611079</v>
       </c>
       <c r="R4" t="n">
-        <v>6954095</v>
+        <v>6953923</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989524</v>
+        <v>124988003</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611045</v>
+        <v>611079</v>
       </c>
       <c r="R5" t="n">
-        <v>6954010</v>
+        <v>6953866</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987406</v>
+        <v>124989858</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611079</v>
+        <v>611048</v>
       </c>
       <c r="R6" t="n">
-        <v>6953923</v>
+        <v>6954042</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988719</v>
+        <v>124988911</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610977</v>
+        <v>611003</v>
       </c>
       <c r="R7" t="n">
-        <v>6953915</v>
+        <v>6953895</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124986204</v>
+        <v>124987437</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611165</v>
+        <v>611077</v>
       </c>
       <c r="R8" t="n">
-        <v>6954011</v>
+        <v>6953924</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1409,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124985975</v>
+        <v>124987900</v>
       </c>
       <c r="B9" t="n">
         <v>90977</v>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611188</v>
+        <v>611079</v>
       </c>
       <c r="R9" t="n">
-        <v>6954015</v>
+        <v>6953885</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988003</v>
+        <v>124986151</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611079</v>
+        <v>611162</v>
       </c>
       <c r="R10" t="n">
-        <v>6953866</v>
+        <v>6953998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986907</v>
+        <v>124986592</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>82597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611061</v>
+        <v>611110</v>
       </c>
       <c r="R11" t="n">
-        <v>6953941</v>
+        <v>6953986</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987571</v>
+        <v>124990391</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,34 +1726,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611100</v>
+        <v>611049</v>
       </c>
       <c r="R12" t="n">
-        <v>6953896</v>
+        <v>6954095</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1791,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987900</v>
+        <v>124985975</v>
       </c>
       <c r="B13" t="n">
         <v>90977</v>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611079</v>
+        <v>611188</v>
       </c>
       <c r="R13" t="n">
-        <v>6953885</v>
+        <v>6954015</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987074</v>
+        <v>124987461</v>
       </c>
       <c r="B14" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611078</v>
+        <v>611070</v>
       </c>
       <c r="R14" t="n">
-        <v>6953994</v>
+        <v>6953915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124986592</v>
+        <v>124987778</v>
       </c>
       <c r="B15" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611110</v>
+        <v>611077</v>
       </c>
       <c r="R15" t="n">
-        <v>6953986</v>
+        <v>6953888</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124988911</v>
+        <v>124987571</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611003</v>
+        <v>611100</v>
       </c>
       <c r="R16" t="n">
-        <v>6953895</v>
+        <v>6953896</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124987461</v>
+        <v>124988719</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,7 +2270,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611070</v>
+        <v>610977</v>
       </c>
       <c r="R17" t="n">
         <v>6953915</v>
@@ -2327,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124987778</v>
+        <v>124987074</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611077</v>
+        <v>611078</v>
       </c>
       <c r="R18" t="n">
-        <v>6953888</v>
+        <v>6953994</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124986151</v>
+        <v>124986204</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,43 +2446,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611162</v>
+        <v>611165</v>
       </c>
       <c r="R19" t="n">
-        <v>6953998</v>
+        <v>6954011</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124986907</v>
+        <v>124988003</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611061</v>
+        <v>611079</v>
       </c>
       <c r="R2" t="n">
-        <v>6953941</v>
+        <v>6953866</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124989524</v>
+        <v>124988911</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611045</v>
+        <v>611003</v>
       </c>
       <c r="R3" t="n">
-        <v>6954010</v>
+        <v>6953895</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987406</v>
+        <v>124987778</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611079</v>
+        <v>611077</v>
       </c>
       <c r="R4" t="n">
-        <v>6953923</v>
+        <v>6953888</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988003</v>
+        <v>124986907</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611079</v>
+        <v>611061</v>
       </c>
       <c r="R5" t="n">
-        <v>6953866</v>
+        <v>6953941</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124989858</v>
+        <v>124986151</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611048</v>
+        <v>611162</v>
       </c>
       <c r="R6" t="n">
-        <v>6954042</v>
+        <v>6953998</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1164,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988911</v>
+        <v>124987074</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611003</v>
+        <v>611078</v>
       </c>
       <c r="R7" t="n">
-        <v>6953895</v>
+        <v>6953994</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987437</v>
+        <v>124987461</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611077</v>
+        <v>611070</v>
       </c>
       <c r="R8" t="n">
-        <v>6953924</v>
+        <v>6953915</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124986151</v>
+        <v>124987571</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,39 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611162</v>
+        <v>611100</v>
       </c>
       <c r="R10" t="n">
-        <v>6953998</v>
+        <v>6953896</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1608,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986592</v>
+        <v>124987406</v>
       </c>
       <c r="B11" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611110</v>
+        <v>611079</v>
       </c>
       <c r="R11" t="n">
-        <v>6953986</v>
+        <v>6953923</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1710,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124990391</v>
+        <v>124986592</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,39 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611049</v>
+        <v>611110</v>
       </c>
       <c r="R12" t="n">
-        <v>6954095</v>
+        <v>6953986</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1791,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124985975</v>
+        <v>124986204</v>
       </c>
       <c r="B13" t="n">
         <v>90977</v>
@@ -1862,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611188</v>
+        <v>611165</v>
       </c>
       <c r="R13" t="n">
-        <v>6954015</v>
+        <v>6954011</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1924,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987461</v>
+        <v>124990391</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,34 +1920,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611070</v>
+        <v>611049</v>
       </c>
       <c r="R14" t="n">
-        <v>6953915</v>
+        <v>6954095</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2000,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987778</v>
+        <v>124985975</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611077</v>
+        <v>611188</v>
       </c>
       <c r="R15" t="n">
-        <v>6953888</v>
+        <v>6954015</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987571</v>
+        <v>124989524</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611100</v>
+        <v>611045</v>
       </c>
       <c r="R16" t="n">
-        <v>6953896</v>
+        <v>6954010</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124988719</v>
+        <v>124989858</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,38 +2232,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610977</v>
+        <v>611048</v>
       </c>
       <c r="R17" t="n">
-        <v>6953915</v>
+        <v>6954042</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124987074</v>
+        <v>124988719</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611078</v>
+        <v>610977</v>
       </c>
       <c r="R18" t="n">
-        <v>6953994</v>
+        <v>6953915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124986204</v>
+        <v>124987437</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611165</v>
+        <v>611077</v>
       </c>
       <c r="R19" t="n">
-        <v>6954011</v>
+        <v>6953924</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987461</v>
+        <v>124987900</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611070</v>
+        <v>611079</v>
       </c>
       <c r="R8" t="n">
-        <v>6953915</v>
+        <v>6953885</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987900</v>
+        <v>124987461</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611079</v>
+        <v>611070</v>
       </c>
       <c r="R9" t="n">
-        <v>6953885</v>
+        <v>6953915</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124988003</v>
+        <v>124987406</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>611079</v>
       </c>
       <c r="R2" t="n">
-        <v>6953866</v>
+        <v>6953923</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124988911</v>
+        <v>124988719</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611003</v>
+        <v>610977</v>
       </c>
       <c r="R3" t="n">
-        <v>6953895</v>
+        <v>6953915</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987778</v>
+        <v>124986204</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611077</v>
+        <v>611165</v>
       </c>
       <c r="R4" t="n">
-        <v>6953888</v>
+        <v>6954011</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124986907</v>
+        <v>124989524</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611061</v>
+        <v>611045</v>
       </c>
       <c r="R5" t="n">
-        <v>6953941</v>
+        <v>6954010</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987074</v>
+        <v>124988911</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611078</v>
+        <v>611003</v>
       </c>
       <c r="R7" t="n">
-        <v>6953994</v>
+        <v>6953895</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987900</v>
+        <v>124986592</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611079</v>
+        <v>611110</v>
       </c>
       <c r="R8" t="n">
-        <v>6953885</v>
+        <v>6953986</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987461</v>
+        <v>124987074</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611070</v>
+        <v>611078</v>
       </c>
       <c r="R9" t="n">
-        <v>6953915</v>
+        <v>6953994</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987571</v>
+        <v>124985975</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611100</v>
+        <v>611188</v>
       </c>
       <c r="R10" t="n">
-        <v>6953896</v>
+        <v>6954015</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987406</v>
+        <v>124990391</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,34 +1614,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611079</v>
+        <v>611049</v>
       </c>
       <c r="R11" t="n">
-        <v>6953923</v>
+        <v>6954095</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124986592</v>
+        <v>124987437</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611110</v>
+        <v>611077</v>
       </c>
       <c r="R12" t="n">
-        <v>6953986</v>
+        <v>6953924</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124986204</v>
+        <v>124987778</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611165</v>
+        <v>611077</v>
       </c>
       <c r="R13" t="n">
-        <v>6954011</v>
+        <v>6953888</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124990391</v>
+        <v>124987571</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,39 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611049</v>
+        <v>611100</v>
       </c>
       <c r="R14" t="n">
-        <v>6954095</v>
+        <v>6953896</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124985975</v>
+        <v>124988003</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611188</v>
+        <v>611079</v>
       </c>
       <c r="R15" t="n">
-        <v>6954015</v>
+        <v>6953866</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124989524</v>
+        <v>124986907</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611045</v>
+        <v>611061</v>
       </c>
       <c r="R16" t="n">
-        <v>6954010</v>
+        <v>6953941</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124989858</v>
+        <v>124987461</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,39 +2236,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611048</v>
+        <v>611070</v>
       </c>
       <c r="R17" t="n">
-        <v>6954042</v>
+        <v>6953915</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2301,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124988719</v>
+        <v>124987900</v>
       </c>
       <c r="B18" t="n">
         <v>90977</v>
@@ -2372,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>610977</v>
+        <v>611079</v>
       </c>
       <c r="R18" t="n">
-        <v>6953915</v>
+        <v>6953885</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2434,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124987437</v>
+        <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,34 +2440,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611077</v>
+        <v>611048</v>
       </c>
       <c r="R19" t="n">
-        <v>6953924</v>
+        <v>6954042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2510,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987406</v>
+        <v>124987437</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611079</v>
+        <v>611077</v>
       </c>
       <c r="R2" t="n">
-        <v>6953923</v>
+        <v>6953924</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124988719</v>
+        <v>124988911</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>91459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610977</v>
+        <v>611003</v>
       </c>
       <c r="R3" t="n">
-        <v>6953915</v>
+        <v>6953895</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124986204</v>
+        <v>124987900</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611165</v>
+        <v>611079</v>
       </c>
       <c r="R4" t="n">
-        <v>6954011</v>
+        <v>6953885</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124989524</v>
+        <v>124988719</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>91131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611045</v>
+        <v>610977</v>
       </c>
       <c r="R5" t="n">
-        <v>6954010</v>
+        <v>6953915</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124986151</v>
+        <v>124986204</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,43 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611162</v>
+        <v>611165</v>
       </c>
       <c r="R6" t="n">
-        <v>6953998</v>
+        <v>6954011</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124988911</v>
+        <v>124986151</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611003</v>
+        <v>611162</v>
       </c>
       <c r="R7" t="n">
-        <v>6953895</v>
+        <v>6953998</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124986592</v>
+        <v>124987778</v>
       </c>
       <c r="B8" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611110</v>
+        <v>611077</v>
       </c>
       <c r="R8" t="n">
-        <v>6953986</v>
+        <v>6953888</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987074</v>
+        <v>124990391</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1410,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611078</v>
+        <v>611049</v>
       </c>
       <c r="R9" t="n">
-        <v>6953994</v>
+        <v>6954095</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124985975</v>
+        <v>124987406</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>91459</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611188</v>
+        <v>611079</v>
       </c>
       <c r="R10" t="n">
-        <v>6954015</v>
+        <v>6953923</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124990391</v>
+        <v>124986907</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,39 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611049</v>
+        <v>611061</v>
       </c>
       <c r="R11" t="n">
-        <v>6954095</v>
+        <v>6953941</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987437</v>
+        <v>124988003</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R12" t="n">
-        <v>6953924</v>
+        <v>6953866</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987778</v>
+        <v>124987571</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91116</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611077</v>
+        <v>611100</v>
       </c>
       <c r="R13" t="n">
-        <v>6953888</v>
+        <v>6953896</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987571</v>
+        <v>124987461</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611100</v>
+        <v>611070</v>
       </c>
       <c r="R14" t="n">
-        <v>6953896</v>
+        <v>6953915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124988003</v>
+        <v>124989524</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>97147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611079</v>
+        <v>611045</v>
       </c>
       <c r="R15" t="n">
-        <v>6953866</v>
+        <v>6954010</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124986907</v>
+        <v>124989858</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,34 +2134,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611061</v>
+        <v>611048</v>
       </c>
       <c r="R16" t="n">
-        <v>6953941</v>
+        <v>6954042</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2194,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124987461</v>
+        <v>124987074</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>88512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611070</v>
+        <v>611078</v>
       </c>
       <c r="R17" t="n">
-        <v>6953915</v>
+        <v>6953994</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124987900</v>
+        <v>124985975</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611079</v>
+        <v>611188</v>
       </c>
       <c r="R18" t="n">
-        <v>6953885</v>
+        <v>6954015</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2424,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124989858</v>
+        <v>124986592</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>82737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,39 +2450,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611048</v>
+        <v>611110</v>
       </c>
       <c r="R19" t="n">
-        <v>6954042</v>
+        <v>6953986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,11 +2510,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987437</v>
+        <v>124987571</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611077</v>
+        <v>611100</v>
       </c>
       <c r="R2" t="n">
-        <v>6953924</v>
+        <v>6953896</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987900</v>
+        <v>124987074</v>
       </c>
       <c r="B4" t="n">
-        <v>91131</v>
+        <v>88512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611079</v>
+        <v>611078</v>
       </c>
       <c r="R4" t="n">
-        <v>6953885</v>
+        <v>6953994</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988719</v>
+        <v>124988003</v>
       </c>
       <c r="B5" t="n">
-        <v>91131</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610977</v>
+        <v>611079</v>
       </c>
       <c r="R5" t="n">
-        <v>6953915</v>
+        <v>6953866</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124986204</v>
+        <v>124987461</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611165</v>
+        <v>611070</v>
       </c>
       <c r="R6" t="n">
-        <v>6954011</v>
+        <v>6953915</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124986151</v>
+        <v>124986204</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>91131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,43 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611162</v>
+        <v>611165</v>
       </c>
       <c r="R7" t="n">
-        <v>6953998</v>
+        <v>6954011</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987778</v>
+        <v>124987900</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R8" t="n">
-        <v>6953888</v>
+        <v>6953885</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124990391</v>
+        <v>124986151</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,16 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611049</v>
+        <v>611162</v>
       </c>
       <c r="R9" t="n">
-        <v>6954095</v>
+        <v>6953998</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1475,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987406</v>
+        <v>124988719</v>
       </c>
       <c r="B10" t="n">
-        <v>91459</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611079</v>
+        <v>610977</v>
       </c>
       <c r="R10" t="n">
-        <v>6953923</v>
+        <v>6953915</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1608,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124986907</v>
+        <v>124989858</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,34 +1614,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611061</v>
+        <v>611048</v>
       </c>
       <c r="R11" t="n">
-        <v>6953941</v>
+        <v>6954042</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124988003</v>
+        <v>124987406</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
         <v>611079</v>
       </c>
       <c r="R12" t="n">
-        <v>6953866</v>
+        <v>6953923</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124987571</v>
+        <v>124986907</v>
       </c>
       <c r="B13" t="n">
-        <v>91116</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611100</v>
+        <v>611061</v>
       </c>
       <c r="R13" t="n">
-        <v>6953896</v>
+        <v>6953941</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987461</v>
+        <v>124987778</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611070</v>
+        <v>611077</v>
       </c>
       <c r="R14" t="n">
-        <v>6953915</v>
+        <v>6953888</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124989858</v>
+        <v>124987437</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,39 +2134,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611048</v>
+        <v>611077</v>
       </c>
       <c r="R16" t="n">
-        <v>6954042</v>
+        <v>6953924</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2199,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124987074</v>
+        <v>124985975</v>
       </c>
       <c r="B17" t="n">
-        <v>88512</v>
+        <v>91131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611078</v>
+        <v>611188</v>
       </c>
       <c r="R17" t="n">
-        <v>6953994</v>
+        <v>6954015</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124985975</v>
+        <v>124990391</v>
       </c>
       <c r="B18" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,38 +2334,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611188</v>
+        <v>611049</v>
       </c>
       <c r="R18" t="n">
-        <v>6954015</v>
+        <v>6954095</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2408,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124986204</v>
+        <v>124987900</v>
       </c>
       <c r="B7" t="n">
         <v>91131</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611165</v>
+        <v>611079</v>
       </c>
       <c r="R7" t="n">
-        <v>6954011</v>
+        <v>6953885</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987900</v>
+        <v>124986204</v>
       </c>
       <c r="B8" t="n">
         <v>91131</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611079</v>
+        <v>611165</v>
       </c>
       <c r="R8" t="n">
-        <v>6953885</v>
+        <v>6954011</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124989524</v>
+        <v>124987437</v>
       </c>
       <c r="B15" t="n">
-        <v>97147</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611045</v>
+        <v>611077</v>
       </c>
       <c r="R15" t="n">
-        <v>6954010</v>
+        <v>6953924</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124987437</v>
+        <v>124989524</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
+        <v>97147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611077</v>
+        <v>611045</v>
       </c>
       <c r="R16" t="n">
-        <v>6953924</v>
+        <v>6954010</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124987571</v>
+        <v>124986204</v>
       </c>
       <c r="B2" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611100</v>
+        <v>611165</v>
       </c>
       <c r="R2" t="n">
-        <v>6953896</v>
+        <v>6954011</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124988911</v>
+        <v>124986592</v>
       </c>
       <c r="B3" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611003</v>
+        <v>611110</v>
       </c>
       <c r="R3" t="n">
-        <v>6953895</v>
+        <v>6953986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124987074</v>
+        <v>124988003</v>
       </c>
       <c r="B4" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611078</v>
+        <v>611079</v>
       </c>
       <c r="R4" t="n">
-        <v>6953994</v>
+        <v>6953866</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124988003</v>
+        <v>124987074</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611079</v>
+        <v>611078</v>
       </c>
       <c r="R5" t="n">
-        <v>6953866</v>
+        <v>6953994</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,11 +1068,6 @@
       <c r="B6" t="n">
         <v>78947</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1185,50 +1160,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124987900</v>
+        <v>124990391</v>
       </c>
       <c r="B7" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611079</v>
+        <v>611049</v>
       </c>
       <c r="R7" t="n">
-        <v>6953885</v>
+        <v>6954095</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,37 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124986204</v>
+        <v>124987778</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611165</v>
+        <v>611077</v>
       </c>
       <c r="R8" t="n">
-        <v>6954011</v>
+        <v>6953888</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,55 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124986151</v>
+        <v>124987900</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611162</v>
+        <v>611079</v>
       </c>
       <c r="R9" t="n">
-        <v>6953998</v>
+        <v>6953885</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,37 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124988719</v>
+        <v>124987571</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610977</v>
+        <v>611100</v>
       </c>
       <c r="R10" t="n">
-        <v>6953915</v>
+        <v>6953896</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124989858</v>
+        <v>124987437</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,39 +1569,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611048</v>
+        <v>611077</v>
       </c>
       <c r="R11" t="n">
-        <v>6954042</v>
+        <v>6953924</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,11 +1660,6 @@
       <c r="B12" t="n">
         <v>91459</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1812,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124986907</v>
+        <v>124988911</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611061</v>
+        <v>611003</v>
       </c>
       <c r="R13" t="n">
-        <v>6953941</v>
+        <v>6953895</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,15 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124987778</v>
+        <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1860,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611077</v>
+        <v>611162</v>
       </c>
       <c r="R14" t="n">
-        <v>6953888</v>
+        <v>6953998</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,37 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124987437</v>
+        <v>124985975</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611077</v>
+        <v>611188</v>
       </c>
       <c r="R15" t="n">
-        <v>6953924</v>
+        <v>6954015</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2118,15 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124989524</v>
+        <v>124988719</v>
       </c>
       <c r="B16" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611045</v>
+        <v>610977</v>
       </c>
       <c r="R16" t="n">
-        <v>6954010</v>
+        <v>6953915</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,15 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124985975</v>
+        <v>124989524</v>
       </c>
       <c r="B17" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611188</v>
+        <v>611045</v>
       </c>
       <c r="R17" t="n">
-        <v>6954015</v>
+        <v>6954010</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,15 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124990391</v>
+        <v>124986907</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,39 +2253,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611049</v>
+        <v>611061</v>
       </c>
       <c r="R18" t="n">
-        <v>6954095</v>
+        <v>6953941</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2403,11 +2313,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,15 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124986592</v>
+        <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,34 +2350,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611110</v>
+        <v>611048</v>
       </c>
       <c r="R19" t="n">
-        <v>6953986</v>
+        <v>6954042</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2510,6 +2415,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1852,7 +1852,7 @@
         <v>124986151</v>
       </c>
       <c r="B14" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>124990391</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>124990391</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>124990391</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>124989858</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124986204</v>
+        <v>124987571</v>
       </c>
       <c r="B2" t="n">
-        <v>91131</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611165</v>
+        <v>611100</v>
       </c>
       <c r="R2" t="n">
-        <v>6954011</v>
+        <v>6953896</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124986592</v>
+        <v>124987074</v>
       </c>
       <c r="B3" t="n">
-        <v>82737</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611110</v>
+        <v>611078</v>
       </c>
       <c r="R3" t="n">
-        <v>6953986</v>
+        <v>6953994</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124988003</v>
+        <v>124987406</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -907,7 +907,7 @@
         <v>611079</v>
       </c>
       <c r="R4" t="n">
-        <v>6953866</v>
+        <v>6953923</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124987074</v>
+        <v>124988911</v>
       </c>
       <c r="B5" t="n">
-        <v>88512</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611078</v>
+        <v>611003</v>
       </c>
       <c r="R5" t="n">
-        <v>6953994</v>
+        <v>6953895</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124987461</v>
+        <v>124987437</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611070</v>
+        <v>611077</v>
       </c>
       <c r="R6" t="n">
-        <v>6953915</v>
+        <v>6953924</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124990391</v>
+        <v>124987778</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611049</v>
+        <v>611077</v>
       </c>
       <c r="R7" t="n">
-        <v>6954095</v>
+        <v>6953888</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1236,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124987778</v>
+        <v>124988003</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611077</v>
+        <v>611079</v>
       </c>
       <c r="R8" t="n">
-        <v>6953888</v>
+        <v>6953866</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124987900</v>
+        <v>124986592</v>
       </c>
       <c r="B9" t="n">
-        <v>91131</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611079</v>
+        <v>611110</v>
       </c>
       <c r="R9" t="n">
-        <v>6953885</v>
+        <v>6953986</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124987571</v>
+        <v>124985975</v>
       </c>
       <c r="B10" t="n">
-        <v>91116</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611100</v>
+        <v>611188</v>
       </c>
       <c r="R10" t="n">
-        <v>6953896</v>
+        <v>6954015</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124987437</v>
+        <v>124986204</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611077</v>
+        <v>611165</v>
       </c>
       <c r="R11" t="n">
-        <v>6953924</v>
+        <v>6954011</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1655,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124987406</v>
+        <v>124987900</v>
       </c>
       <c r="B12" t="n">
-        <v>91459</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,7 +1683,7 @@
         <v>611079</v>
       </c>
       <c r="R12" t="n">
-        <v>6953923</v>
+        <v>6953885</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1752,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124988911</v>
+        <v>124988719</v>
       </c>
       <c r="B13" t="n">
-        <v>91459</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611003</v>
+        <v>610977</v>
       </c>
       <c r="R13" t="n">
-        <v>6953895</v>
+        <v>6953915</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1849,50 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124986151</v>
+        <v>124987461</v>
       </c>
       <c r="B14" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611162</v>
+        <v>611070</v>
       </c>
       <c r="R14" t="n">
-        <v>6953998</v>
+        <v>6953915</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1951,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124985975</v>
+        <v>124986907</v>
       </c>
       <c r="B15" t="n">
-        <v>91131</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611188</v>
+        <v>611061</v>
       </c>
       <c r="R15" t="n">
-        <v>6954015</v>
+        <v>6953941</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2048,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124988719</v>
+        <v>124986151</v>
       </c>
       <c r="B16" t="n">
-        <v>91131</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,34 +2044,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>610977</v>
+        <v>611162</v>
       </c>
       <c r="R16" t="n">
-        <v>6953915</v>
+        <v>6953998</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2145,45 +2135,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124989524</v>
+        <v>124989858</v>
       </c>
       <c r="B17" t="n">
-        <v>97147</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611045</v>
+        <v>611048</v>
       </c>
       <c r="R17" t="n">
-        <v>6954010</v>
+        <v>6954042</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2216,6 +2211,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124986907</v>
+        <v>124990391</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,34 +2253,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611061</v>
+        <v>611049</v>
       </c>
       <c r="R18" t="n">
-        <v>6953941</v>
+        <v>6954095</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2313,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2339,50 +2349,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124989858</v>
+        <v>124989524</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Per-Ersslåtten, Per-Ersslåtten, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611048</v>
+        <v>611045</v>
       </c>
       <c r="R19" t="n">
-        <v>6954042</v>
+        <v>6954010</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 11025-2025 artfynd.xlsx
+++ b/artfynd/A 11025-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987437</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988003</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986592</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124985975</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986204</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124988719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124987461</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986907</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124986151</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124989858</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124990391</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,8 +2533,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124989524</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>